--- a/lib/Component_library.xlsx
+++ b/lib/Component_library.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\loube\Desktop\Lib data\lib\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{80817D52-A5C4-4955-98C7-12DA7863D8B2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{026704EC-66D2-4E2F-9C5A-748990760DD3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="238" uniqueCount="188">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="251" uniqueCount="197">
   <si>
     <t>Manufacturer Ref</t>
   </si>
@@ -584,13 +584,40 @@
   </si>
   <si>
     <t>511-STM32C552CEU6</t>
+  </si>
+  <si>
+    <t>C49164922</t>
+  </si>
+  <si>
+    <t>JIERR</t>
+  </si>
+  <si>
+    <t>220m</t>
+  </si>
+  <si>
+    <t>RES 220mΩ ±1% 2W 2512</t>
+  </si>
+  <si>
+    <t>JIERR JER2512F2R220</t>
+  </si>
+  <si>
+    <t>2512</t>
+  </si>
+  <si>
+    <t>RES 120mΩ ±1% 3W 2512</t>
+  </si>
+  <si>
+    <t>C49164917</t>
+  </si>
+  <si>
+    <t>JIERR JER2512F3R120</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="x14ac x16r2 xr xr9">
-  <fonts count="13" x14ac:knownFonts="1">
+  <fonts count="17" x14ac:knownFonts="1">
     <font>
       <sz val="10"/>
       <color rgb="FF000000"/>
@@ -658,8 +685,37 @@
       <name val="Arial"/>
     </font>
     <font>
+      <u/>
+      <sz val="10"/>
+      <color theme="10"/>
+      <name val="Arial"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <sz val="12"/>
       <color rgb="FF333333"/>
+      <name val="Arial"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FF000000"/>
+      <name val="Arial"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="Arial"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="10"/>
+      <color theme="10"/>
       <name val="Arial"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -746,10 +802,11 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="22">
+  <cellXfs count="26">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="49" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -807,9 +864,16 @@
     </xf>
     <xf numFmtId="49" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="1"/>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="49" fontId="15" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="1" applyFont="1"/>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="2">
+    <cellStyle name="Lien hypertexte" xfId="1" builtinId="8"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="4">
@@ -2185,17 +2249,53 @@
       <c r="J39" s="12"/>
     </row>
     <row r="40" spans="1:10" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B40" s="5"/>
+      <c r="A40" t="s">
+        <v>192</v>
+      </c>
+      <c r="B40" s="5" t="s">
+        <v>143</v>
+      </c>
+      <c r="C40" t="s">
+        <v>191</v>
+      </c>
+      <c r="D40" s="23" t="s">
+        <v>190</v>
+      </c>
+      <c r="E40">
+        <v>2512</v>
+      </c>
+      <c r="H40" s="22" t="s">
+        <v>188</v>
+      </c>
+      <c r="I40" t="s">
+        <v>189</v>
+      </c>
       <c r="J40" s="8"/>
     </row>
     <row r="41" spans="1:10" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A41" s="5"/>
-      <c r="B41" s="5"/>
-      <c r="C41" s="5"/>
-      <c r="D41" s="10"/>
-      <c r="E41" s="10"/>
+      <c r="A41" s="5" t="s">
+        <v>196</v>
+      </c>
+      <c r="B41" s="5" t="s">
+        <v>143</v>
+      </c>
+      <c r="C41" s="5" t="s">
+        <v>194</v>
+      </c>
+      <c r="D41" s="24" t="s">
+        <v>145</v>
+      </c>
+      <c r="E41" s="10" t="s">
+        <v>193</v>
+      </c>
       <c r="F41" s="5"/>
       <c r="G41" s="5"/>
+      <c r="H41" s="25" t="s">
+        <v>195</v>
+      </c>
+      <c r="I41" s="23" t="s">
+        <v>189</v>
+      </c>
       <c r="J41" s="8"/>
     </row>
     <row r="42" spans="1:10" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
@@ -7383,10 +7483,12 @@
     <hyperlink ref="H36" r:id="rId31" xr:uid="{00000000-0004-0000-0000-00001E000000}"/>
     <hyperlink ref="H37" r:id="rId32" xr:uid="{00000000-0004-0000-0000-00001F000000}"/>
     <hyperlink ref="H38" r:id="rId33" xr:uid="{00000000-0004-0000-0000-000020000000}"/>
+    <hyperlink ref="H40" r:id="rId34" xr:uid="{34EA4375-CD82-4844-8EF1-B5D55C408341}"/>
+    <hyperlink ref="H41" r:id="rId35" xr:uid="{5722FFB7-2B7A-4328-ADA3-9C305D5B943B}"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <tableParts count="1">
-    <tablePart r:id="rId34"/>
+    <tablePart r:id="rId36"/>
   </tableParts>
 </worksheet>
 </file>
--- a/lib/Component_library.xlsx
+++ b/lib/Component_library.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\loube\Desktop\Lib data\lib\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{026704EC-66D2-4E2F-9C5A-748990760DD3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CE930C2A-E3A4-4D72-B7CA-E59B1F5190FC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -601,9 +601,6 @@
     <t>JIERR JER2512F2R220</t>
   </si>
   <si>
-    <t>2512</t>
-  </si>
-  <si>
     <t>RES 120mΩ ±1% 3W 2512</t>
   </si>
   <si>
@@ -611,6 +608,9 @@
   </si>
   <si>
     <t>JIERR JER2512F3R120</t>
+  </si>
+  <si>
+    <t>tof</t>
   </si>
 </sst>
 </file>
@@ -806,7 +806,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="26">
+  <cellXfs count="27">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="49" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -871,6 +871,9 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Lien hypertexte" xfId="1" builtinId="8"/>
@@ -2232,7 +2235,9 @@
       <c r="C39" s="5" t="s">
         <v>182</v>
       </c>
-      <c r="D39" s="18"/>
+      <c r="D39" s="18" t="s">
+        <v>196</v>
+      </c>
       <c r="E39" s="10" t="s">
         <v>183</v>
       </c>
@@ -2274,24 +2279,24 @@
     </row>
     <row r="41" spans="1:10" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A41" s="5" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="B41" s="5" t="s">
         <v>143</v>
       </c>
       <c r="C41" s="5" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="D41" s="24" t="s">
         <v>145</v>
       </c>
-      <c r="E41" s="10" t="s">
-        <v>193</v>
+      <c r="E41" s="26">
+        <v>2512</v>
       </c>
       <c r="F41" s="5"/>
       <c r="G41" s="5"/>
       <c r="H41" s="25" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="I41" s="23" t="s">
         <v>189</v>
